--- a/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>LEGN</t>
   </si>
@@ -656,52 +656,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -711,33 +711,36 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>285100</v>
+      </c>
+      <c r="E8" s="3">
         <v>117000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>68800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>60000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23600</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -747,18 +750,21 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E9" s="3">
         <v>65400</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,18 +789,21 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>140900</v>
+      </c>
+      <c r="E10" s="3">
         <v>51600</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,9 +828,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,32 +848,33 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>382200</v>
+      </c>
+      <c r="E12" s="3">
         <v>335600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>313300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>232200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>161900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>60600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8200</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,9 +884,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,9 +923,12 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -943,9 +962,12 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -979,9 +1001,12 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,32 +1018,33 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>727400</v>
+      </c>
+      <c r="E17" s="3">
         <v>575100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>462800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>384800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>194300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>64600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9800</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,33 +1054,36 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-442200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-458100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-394000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-309800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-134300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13800</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1064,9 +1093,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,32 +1113,33 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-77900</v>
+      </c>
+      <c r="E20" s="3">
         <v>23100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>13900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1116,33 +1149,36 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-416500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-392400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-298200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-123000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14100</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,32 +1188,35 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>10800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1188,33 +1227,36 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-520100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-445700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-407200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-308300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-127300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13800</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,33 +1266,36 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-41900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-25700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4500</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,9 +1305,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,33 +1344,36 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-518300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-446300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-403600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-266400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-101600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9400</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1332,33 +1383,36 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-518300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-446300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-403600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-266400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-101600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9400</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1368,9 +1422,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,33 +1578,36 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-23100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-13900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,33 +1617,36 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-518300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-446300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-403600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-266400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-101600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9400</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,9 +1656,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,33 +1695,36 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-518300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-446300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-403600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-266400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-101600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9400</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,38 +1734,41 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1697,9 +1778,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,32 +1815,33 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1277700</v>
+      </c>
+      <c r="E41" s="3">
         <v>786000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>688900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>455700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>210200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,32 +1851,35 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E42" s="3">
         <v>240900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>194900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>50400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>75800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6300</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1801,33 +1890,36 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E43" s="3">
         <v>45500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>58300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>82500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>60000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>228000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,32 +1929,35 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E44" s="3">
         <v>10400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1100</v>
       </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="J44" s="3">
+        <v>0</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1873,33 +1968,36 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E45" s="3">
         <v>16300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>83200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1909,33 +2007,36 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1497800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1099100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>949900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>593900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>212000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>327000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>230900</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,32 +2046,35 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>500</v>
+      </c>
+      <c r="E47" s="3">
         <v>900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1200</v>
       </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="J47" s="3">
+        <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1981,33 +2085,36 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E48" s="3">
         <v>160800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>140800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>111900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>152400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,32 +2124,35 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E49" s="3">
         <v>3400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1000</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2053,9 +2163,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,33 +2241,36 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E52" s="3">
         <v>66800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>68900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,9 +2280,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,33 +2319,36 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1848600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1331000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1119500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>722100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>292600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>429000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>238700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2233,9 +2358,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,32 +2395,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E57" s="3">
         <v>32900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>80400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2301,33 +2431,36 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2337,33 +2470,36 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E59" s="3">
         <v>261300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>221300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>163900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>129900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>151200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>47700</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,33 +2509,36 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>216400</v>
+      </c>
+      <c r="E60" s="3">
         <v>297800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>229200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>115600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>94200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>159200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,33 +2548,36 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>325500</v>
+      </c>
+      <c r="E61" s="3">
         <v>281000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>122100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2445,33 +2587,36 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E62" s="3">
         <v>7900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>281900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>319800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>257300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>174200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,33 +2743,36 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>597200</v>
+      </c>
+      <c r="E66" s="3">
         <v>586700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>353500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>124300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>141300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>420400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>226500</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2625,9 +2782,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,33 +2955,36 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1251300</v>
+      </c>
+      <c r="E72" s="3">
         <v>744300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>765900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>597700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>151300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2821,9 +2994,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,33 +3111,36 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1251400</v>
+      </c>
+      <c r="E76" s="3">
         <v>744300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>765900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>597800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>151300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12200</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,9 +3150,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,38 +3189,41 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3042,33 +3233,36 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-518300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-446300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-403600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-266400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-101600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9400</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3078,9 +3272,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,32 +3292,33 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>18400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3130,9 +3328,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,33 +3523,36 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-393300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-201300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-198500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-223000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-83100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>307700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,9 +3562,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,32 +3582,33 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3398,9 +3618,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,33 +3696,36 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-195000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-58700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-102300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,9 +3735,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,33 +3908,36 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>791500</v>
+      </c>
+      <c r="E100" s="3">
         <v>378000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>626700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>618900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>14700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3300</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3702,32 +3947,35 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2500</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3738,33 +3986,36 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E102" s="3">
         <v>97100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>233200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>372300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-126800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>208100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3774,7 +4025,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>LEGN</t>
   </si>
@@ -1025,13 +1025,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>727400</v>
+        <v>813100</v>
       </c>
       <c r="E17" s="3">
-        <v>575100</v>
+        <v>554200</v>
       </c>
       <c r="F17" s="3">
-        <v>462800</v>
+        <v>469000</v>
       </c>
       <c r="G17" s="3">
         <v>384800</v>
@@ -1064,13 +1064,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-442200</v>
+        <v>-528000</v>
       </c>
       <c r="E18" s="3">
-        <v>-458100</v>
+        <v>-437200</v>
       </c>
       <c r="F18" s="3">
-        <v>-394000</v>
+        <v>-400200</v>
       </c>
       <c r="G18" s="3">
         <v>-309800</v>
@@ -1120,13 +1120,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-77900</v>
+        <v>29600</v>
       </c>
       <c r="E20" s="3">
-        <v>23100</v>
+        <v>2200</v>
       </c>
       <c r="F20" s="3">
-        <v>-12300</v>
+        <v>-6100</v>
       </c>
       <c r="G20" s="3">
         <v>1800</v>
@@ -1158,8 +1158,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-477900</v>
       </c>
       <c r="E21" s="3">
         <v>-416500</v>
@@ -1171,7 +1171,7 @@
         <v>-298200</v>
       </c>
       <c r="H21" s="3">
-        <v>-123000</v>
+        <v>-121800</v>
       </c>
       <c r="I21" s="3">
         <v>100</v>
@@ -1197,8 +1197,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>21800</v>
       </c>
       <c r="E22" s="3">
         <v>10800</v>
@@ -1588,13 +1588,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>77900</v>
+        <v>-29600</v>
       </c>
       <c r="E32" s="3">
-        <v>-23100</v>
+        <v>-2200</v>
       </c>
       <c r="F32" s="3">
-        <v>12300</v>
+        <v>6100</v>
       </c>
       <c r="G32" s="3">
         <v>-1800</v>
@@ -1900,7 +1900,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100000</v>
+        <v>157100</v>
       </c>
       <c r="E43" s="3">
         <v>45500</v>
@@ -1978,7 +1978,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>69300</v>
+        <v>12200</v>
       </c>
       <c r="E45" s="3">
         <v>16300</v>
@@ -2056,7 +2056,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E47" s="3">
         <v>900</v>
@@ -2251,7 +2251,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>157100</v>
+        <v>156800</v>
       </c>
       <c r="E52" s="3">
         <v>66800</v>
@@ -2402,7 +2402,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>153000</v>
+        <v>20200</v>
       </c>
       <c r="E57" s="3">
         <v>32900</v>
@@ -2480,7 +2480,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>60300</v>
+        <v>193100</v>
       </c>
       <c r="E59" s="3">
         <v>261300</v>
@@ -3298,8 +3298,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>20500</v>
       </c>
       <c r="E83" s="3">
         <v>18400</v>
@@ -3311,7 +3311,7 @@
         <v>9900</v>
       </c>
       <c r="H83" s="3">
-        <v>4100</v>
+        <v>5300</v>
       </c>
       <c r="I83" s="3">
         <v>1700</v>
@@ -3588,8 +3588,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-20100</v>
       </c>
       <c r="E91" s="3">
         <v>-20900</v>
@@ -3996,7 +3996,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>491000</v>
+        <v>491700</v>
       </c>
       <c r="E102" s="3">
         <v>97100</v>

--- a/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>LEGN</t>
   </si>
@@ -662,7 +662,9 @@
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -694,7 +696,7 @@
         <v>44196</v>
       </c>
       <c r="H7" s="2">
-        <v>43830</v>
+        <v>43831</v>
       </c>
       <c r="I7" s="2">
         <v>43465</v>
@@ -733,13 +735,13 @@
         <v>75000</v>
       </c>
       <c r="H8" s="3">
-        <v>60000</v>
+        <v>61800</v>
       </c>
       <c r="I8" s="3">
-        <v>49100</v>
+        <v>49500</v>
       </c>
       <c r="J8" s="3">
-        <v>23600</v>
+        <v>23700</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -760,16 +762,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>144200</v>
+        <v>526400</v>
       </c>
       <c r="E9" s="3">
-        <v>65400</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+        <v>401000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>313300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>232200</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -799,25 +801,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>140900</v>
+        <v>-241300</v>
       </c>
       <c r="E10" s="3">
-        <v>51600</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>-284000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-244500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-157200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>61800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>49500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>23700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -933,25 +935,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -972,25 +974,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1025,16 +1027,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>813100</v>
+        <v>727400</v>
       </c>
       <c r="E17" s="3">
-        <v>554200</v>
+        <v>575100</v>
       </c>
       <c r="F17" s="3">
-        <v>469000</v>
+        <v>462800</v>
       </c>
       <c r="G17" s="3">
-        <v>384800</v>
+        <v>304900</v>
       </c>
       <c r="H17" s="3">
         <v>194300</v>
@@ -1064,25 +1066,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-528000</v>
+        <v>-442200</v>
       </c>
       <c r="E18" s="3">
-        <v>-437200</v>
+        <v>-458100</v>
       </c>
       <c r="F18" s="3">
-        <v>-400200</v>
+        <v>-394000</v>
       </c>
       <c r="G18" s="3">
-        <v>-309800</v>
+        <v>-229900</v>
       </c>
       <c r="H18" s="3">
-        <v>-134300</v>
+        <v>-132500</v>
       </c>
       <c r="I18" s="3">
-        <v>-15400</v>
+        <v>-15100</v>
       </c>
       <c r="J18" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1120,25 +1122,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>29600</v>
+        <v>111000</v>
       </c>
       <c r="E20" s="3">
-        <v>2200</v>
+        <v>-14800</v>
       </c>
       <c r="F20" s="3">
-        <v>-6100</v>
+        <v>12300</v>
       </c>
       <c r="G20" s="3">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="H20" s="3">
-        <v>7200</v>
+        <v>-400</v>
       </c>
       <c r="I20" s="3">
-        <v>13900</v>
+        <v>-7200</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1159,25 +1161,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-477900</v>
+        <v>-542500</v>
       </c>
       <c r="E21" s="3">
-        <v>-416500</v>
+        <v>-433100</v>
       </c>
       <c r="F21" s="3">
-        <v>-392400</v>
+        <v>-398200</v>
       </c>
       <c r="G21" s="3">
-        <v>-298200</v>
+        <v>-224800</v>
       </c>
       <c r="H21" s="3">
-        <v>-121800</v>
+        <v>-129000</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
+        <v>-7000</v>
       </c>
       <c r="J21" s="3">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1396,7 +1398,7 @@
         <v>-518300</v>
       </c>
       <c r="E27" s="3">
-        <v>-446300</v>
+        <v>-446400</v>
       </c>
       <c r="F27" s="3">
         <v>-403600</v>
@@ -1588,25 +1590,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-29600</v>
+        <v>-111000</v>
       </c>
       <c r="E32" s="3">
-        <v>-2200</v>
+        <v>14800</v>
       </c>
       <c r="F32" s="3">
-        <v>6100</v>
+        <v>-12300</v>
       </c>
       <c r="G32" s="3">
-        <v>-1800</v>
+        <v>-1200</v>
       </c>
       <c r="H32" s="3">
-        <v>-7200</v>
+        <v>400</v>
       </c>
       <c r="I32" s="3">
-        <v>-13900</v>
+        <v>7200</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1761,7 +1763,7 @@
         <v>44196</v>
       </c>
       <c r="H38" s="2">
-        <v>43830</v>
+        <v>43831</v>
       </c>
       <c r="I38" s="2">
         <v>43465</v>
@@ -1861,22 +1863,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>31400</v>
+        <v>31000</v>
       </c>
       <c r="E42" s="3">
-        <v>240900</v>
+        <v>239600</v>
       </c>
       <c r="F42" s="3">
-        <v>194900</v>
+        <v>193500</v>
       </c>
       <c r="G42" s="3">
-        <v>50400</v>
+        <v>50000</v>
       </c>
       <c r="H42" s="3">
-        <v>75800</v>
+        <v>75600</v>
       </c>
       <c r="I42" s="3">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1903,22 +1905,22 @@
         <v>157100</v>
       </c>
       <c r="E43" s="3">
-        <v>45500</v>
+        <v>44500</v>
       </c>
       <c r="F43" s="3">
-        <v>58300</v>
+        <v>58500</v>
       </c>
       <c r="G43" s="3">
-        <v>82500</v>
+        <v>82600</v>
       </c>
       <c r="H43" s="3">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="I43" s="3">
-        <v>26200</v>
+        <v>108600</v>
       </c>
       <c r="J43" s="3">
-        <v>228000</v>
+        <v>228700</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1948,7 +1950,7 @@
         <v>1700</v>
       </c>
       <c r="G44" s="3">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="H44" s="3">
         <v>1200</v>
@@ -1978,25 +1980,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12200</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>16300</v>
+        <v>1300</v>
       </c>
       <c r="F45" s="3">
-        <v>5900</v>
+        <v>1400</v>
       </c>
       <c r="G45" s="3">
-        <v>13500</v>
+        <v>400</v>
       </c>
       <c r="H45" s="3">
-        <v>21700</v>
+        <v>300</v>
       </c>
       <c r="I45" s="3">
-        <v>83200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
+        <v>300</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2056,25 +2058,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>900</v>
+        <v>4400</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>4700</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2107,7 +2109,7 @@
         <v>111900</v>
       </c>
       <c r="H48" s="3">
-        <v>152400</v>
+        <v>73000</v>
       </c>
       <c r="I48" s="3">
         <v>31900</v>
@@ -2146,7 +2148,7 @@
         <v>2900</v>
       </c>
       <c r="H49" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -2251,25 +2253,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>156800</v>
+        <v>152900</v>
       </c>
       <c r="E52" s="3">
-        <v>66800</v>
+        <v>67300</v>
       </c>
       <c r="F52" s="3">
-        <v>22000</v>
+        <v>19400</v>
       </c>
       <c r="G52" s="3">
-        <v>13200</v>
+        <v>13400</v>
       </c>
       <c r="H52" s="3">
-        <v>6400</v>
+        <v>7100</v>
       </c>
       <c r="I52" s="3">
-        <v>68900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>4900</v>
+        <v>1200</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2411,13 +2413,13 @@
         <v>7000</v>
       </c>
       <c r="G57" s="3">
-        <v>10100</v>
+        <v>4900</v>
       </c>
       <c r="H57" s="3">
-        <v>80400</v>
+        <v>9600</v>
       </c>
       <c r="I57" s="3">
-        <v>7600</v>
+        <v>7300</v>
       </c>
       <c r="J57" s="3">
         <v>4300</v>
@@ -2456,7 +2458,7 @@
         <v>1000</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
@@ -2480,25 +2482,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>193100</v>
+        <v>87700</v>
       </c>
       <c r="E59" s="3">
-        <v>261300</v>
+        <v>108600</v>
       </c>
       <c r="F59" s="3">
-        <v>221300</v>
+        <v>116900</v>
       </c>
       <c r="G59" s="3">
-        <v>163900</v>
+        <v>34500</v>
       </c>
       <c r="H59" s="3">
-        <v>129900</v>
+        <v>83600</v>
       </c>
       <c r="I59" s="3">
-        <v>151200</v>
+        <v>148800</v>
       </c>
       <c r="J59" s="3">
-        <v>47700</v>
+        <v>47400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2597,25 +2599,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>55300</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>7900</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>2300</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>281900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>319800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>257300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>174200</v>
+        <v>600</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2965,25 +2967,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1251300</v>
+        <v>-1484700</v>
       </c>
       <c r="E72" s="3">
-        <v>744300</v>
+        <v>-966500</v>
       </c>
       <c r="F72" s="3">
-        <v>765900</v>
+        <v>-520100</v>
       </c>
       <c r="G72" s="3">
-        <v>597700</v>
+        <v>-116500</v>
       </c>
       <c r="H72" s="3">
-        <v>151300</v>
+        <v>149800</v>
       </c>
       <c r="I72" s="3">
-        <v>8600</v>
+        <v>5700</v>
       </c>
       <c r="J72" s="3">
-        <v>12100</v>
+        <v>8500</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3216,7 +3218,7 @@
         <v>44196</v>
       </c>
       <c r="H80" s="2">
-        <v>43830</v>
+        <v>43831</v>
       </c>
       <c r="I80" s="2">
         <v>43465</v>
@@ -3299,19 +3301,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>20500</v>
+        <v>18500</v>
       </c>
       <c r="E83" s="3">
-        <v>18400</v>
+        <v>15900</v>
       </c>
       <c r="F83" s="3">
-        <v>13900</v>
+        <v>12500</v>
       </c>
       <c r="G83" s="3">
-        <v>9900</v>
+        <v>9700</v>
       </c>
       <c r="H83" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="I83" s="3">
         <v>1700</v>
@@ -3595,13 +3597,13 @@
         <v>-20900</v>
       </c>
       <c r="F91" s="3">
-        <v>-43900</v>
+        <v>-42200</v>
       </c>
       <c r="G91" s="3">
-        <v>-45700</v>
+        <v>-26300</v>
       </c>
       <c r="H91" s="3">
-        <v>-38600</v>
+        <v>-26800</v>
       </c>
       <c r="I91" s="3">
         <v>-21000</v>

--- a/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>LEGN</t>
   </si>
@@ -656,57 +656,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43831</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -716,36 +716,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>627200</v>
+      </c>
+      <c r="E8" s="3">
         <v>285100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>117000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>68800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>61800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23700</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -755,27 +758,30 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>648100</v>
+      </c>
+      <c r="E9" s="3">
         <v>526400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>401000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>313300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>232200</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -794,36 +800,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-241300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-284000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-244500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-157200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>61800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>49500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -833,9 +842,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,35 +863,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>413500</v>
+      </c>
+      <c r="E12" s="3">
         <v>382200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>335600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>313300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>232200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>161900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>60600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -889,9 +902,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,35 +944,38 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>80000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -967,36 +986,39 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E15" s="3">
         <v>10700</v>
       </c>
-      <c r="E15" s="3">
-        <v>10200</v>
-      </c>
       <c r="F15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G15" s="3">
         <v>8100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1006,9 +1028,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1021,35 +1046,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>932400</v>
+      </c>
+      <c r="E17" s="3">
         <v>727400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>575100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>462800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>304900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>194300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>64600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9800</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1059,36 +1085,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-305100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-442200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-458100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-394000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-229900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-132500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1098,9 +1127,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1116,34 +1148,35 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-111900</v>
+      </c>
+      <c r="E20" s="3">
         <v>111000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-14800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1154,36 +1187,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-182400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-542500</v>
       </c>
-      <c r="E21" s="3">
-        <v>-433100</v>
-      </c>
       <c r="F21" s="3">
+        <v>-430600</v>
+      </c>
+      <c r="G21" s="3">
         <v>-398200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-224800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-129000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1193,35 +1229,38 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E22" s="3">
         <v>21800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1232,36 +1271,39 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-158100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-520100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-445700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-407200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-308300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-127300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1271,36 +1313,39 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-41900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-25700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4500</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1310,9 +1355,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1349,36 +1397,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-518300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-446300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-403600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-266400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-101600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1388,36 +1439,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-518300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-446400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-403600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-266400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-101600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1427,9 +1481,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1466,9 +1523,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1505,9 +1565,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1544,9 +1607,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1583,35 +1649,38 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-111000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>14800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1622,36 +1691,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-518300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-446300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-403600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-266400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-101600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1661,9 +1733,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1700,36 +1775,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-518300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-446300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-403600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-266400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-101600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,41 +1817,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43831</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1783,9 +1864,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1801,8 +1885,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1818,35 +1903,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>286700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1277700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>786000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>688900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>455700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>83400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>210200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1856,35 +1942,38 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>835900</v>
+      </c>
+      <c r="E42" s="3">
         <v>31000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>239600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>193500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>50000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>75600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -1895,36 +1984,39 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E43" s="3">
         <v>157100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>44500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>58500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>82600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>108600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>228700</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1934,35 +2026,38 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E44" s="3">
         <v>19400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1100</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -1973,32 +2068,35 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>300</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2012,36 +2110,39 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1283900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1497800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1099100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>949900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>593900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>212000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>327000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>230900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2051,24 +2152,27 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>4400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="E47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>4700</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,36 +2194,39 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E48" s="3">
         <v>189200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>160800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>140800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>111900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2129,35 +2236,38 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E49" s="3">
         <v>4100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2168,9 +2278,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2207,9 +2320,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2246,33 +2362,36 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>152900</v>
+        <v>178500</v>
       </c>
       <c r="E52" s="3">
+        <v>153200</v>
+      </c>
+      <c r="F52" s="3">
         <v>67300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,9 +2404,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2324,36 +2446,39 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1670200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1848600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1331000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1119500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>722100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>292600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>429000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>238700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,9 +2488,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2381,8 +2509,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2398,35 +2527,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>20200</v>
+        <v>38600</v>
       </c>
       <c r="E57" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F57" s="3">
         <v>32900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,36 +2566,39 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,36 +2608,39 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>87700</v>
+        <v>169800</v>
       </c>
       <c r="E59" s="3">
+        <v>121000</v>
+      </c>
+      <c r="F59" s="3">
         <v>108600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>116900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>83600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>148800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>47400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2514,36 +2650,39 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E60" s="3">
         <v>216400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>297800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>229200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>115600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>94200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>159200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2553,36 +2692,39 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>345800</v>
+      </c>
+      <c r="E61" s="3">
         <v>325500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>281000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>122100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2592,27 +2734,30 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,9 +2776,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2670,9 +2818,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2709,9 +2860,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2748,36 +2902,39 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>629600</v>
+      </c>
+      <c r="E66" s="3">
         <v>597200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>586700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>353500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>124300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>141300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>420400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>226500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2787,9 +2944,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2805,8 +2965,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2843,9 +3004,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2882,9 +3046,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2921,9 +3088,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2960,36 +3130,39 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1661700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1484700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-966500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-520100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-116500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>149800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2999,9 +3172,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3038,9 +3214,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3077,9 +3256,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3116,36 +3298,39 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1040500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1251400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>744300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>765900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>597800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>151300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,9 +3340,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3194,41 +3382,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43831</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3238,36 +3429,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-518300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-446300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-403600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-266400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-101600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3277,9 +3471,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3295,35 +3492,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E83" s="3">
         <v>18500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3333,9 +3531,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3372,9 +3573,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3411,9 +3615,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3450,9 +3657,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3489,9 +3699,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3528,36 +3741,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-144000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-393300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-201300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-198500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-223000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-83100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>307700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3567,9 +3783,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3585,35 +3804,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-42200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,9 +3843,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3662,9 +3885,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3701,36 +3927,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-850500</v>
+      </c>
+      <c r="E94" s="3">
         <v>92800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-195000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-102300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3740,9 +3969,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3758,8 +3990,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3796,9 +4029,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3835,9 +4071,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3874,9 +4113,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3913,36 +4155,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E100" s="3">
         <v>791500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>378000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>626700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>618900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>14700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3300</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3952,35 +4197,38 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2500</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -3991,36 +4239,39 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-991000</v>
+      </c>
+      <c r="E102" s="3">
         <v>491700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>97100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>233200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>372300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-126800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>208100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4030,7 +4281,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
@@ -957,10 +957,10 @@
         <v>4400</v>
       </c>
       <c r="E14" s="3">
-        <v>-400</v>
+        <v>-700</v>
       </c>
       <c r="F14" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="G14" s="3">
         <v>1000</v>
@@ -1155,13 +1155,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-111900</v>
+        <v>-111800</v>
       </c>
       <c r="E20" s="3">
-        <v>111000</v>
+        <v>111300</v>
       </c>
       <c r="F20" s="3">
-        <v>-14800</v>
+        <v>-14300</v>
       </c>
       <c r="G20" s="3">
         <v>12300</v>
@@ -1200,10 +1200,10 @@
         <v>-182400</v>
       </c>
       <c r="E21" s="3">
-        <v>-542500</v>
+        <v>-542700</v>
       </c>
       <c r="F21" s="3">
-        <v>-430600</v>
+        <v>-431100</v>
       </c>
       <c r="G21" s="3">
         <v>-398200</v>
@@ -1659,13 +1659,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>111900</v>
+        <v>111800</v>
       </c>
       <c r="E32" s="3">
-        <v>-111000</v>
+        <v>-111300</v>
       </c>
       <c r="F32" s="3">
-        <v>14800</v>
+        <v>14300</v>
       </c>
       <c r="G32" s="3">
         <v>-12300</v>

--- a/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>LEGN</t>
   </si>
@@ -656,60 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43831</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -719,39 +719,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>627200</v>
+        <v>1028900</v>
       </c>
       <c r="E8" s="3">
+        <v>627300</v>
+      </c>
+      <c r="F8" s="3">
         <v>285100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>117000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>68800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>75000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>61800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -761,30 +764,33 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>822800</v>
+      </c>
+      <c r="E9" s="3">
         <v>648100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>526400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>401000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>313300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>232200</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,39 +809,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-20900</v>
+        <v>206100</v>
       </c>
       <c r="E10" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="F10" s="3">
         <v>-241300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-284000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-244500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-157200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>61800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>49500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -845,9 +854,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,38 +876,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>414700</v>
+      </c>
+      <c r="E12" s="3">
         <v>413500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>382200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>335600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>313300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>232200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>161900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>60600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -905,9 +918,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,38 +963,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>4400</v>
       </c>
-      <c r="E14" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>-600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>80000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -989,39 +1008,42 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10900</v>
+        <v>9400</v>
       </c>
       <c r="E15" s="3">
         <v>10700</v>
       </c>
       <c r="F15" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G15" s="3">
         <v>12600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1031,9 +1053,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,38 +1072,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1165400</v>
+      </c>
+      <c r="E17" s="3">
         <v>932400</v>
       </c>
-      <c r="E17" s="3">
-        <v>727400</v>
-      </c>
       <c r="F17" s="3">
+        <v>813200</v>
+      </c>
+      <c r="G17" s="3">
         <v>575100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>462800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>304900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>194300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>64600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,39 +1114,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-136500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-305100</v>
       </c>
-      <c r="E18" s="3">
-        <v>-442200</v>
-      </c>
       <c r="F18" s="3">
+        <v>-528100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-458100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-394000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-229900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-132500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1130,9 +1159,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1149,37 +1181,38 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-111800</v>
       </c>
-      <c r="E20" s="3">
-        <v>111300</v>
-      </c>
       <c r="F20" s="3">
+        <v>24800</v>
+      </c>
+      <c r="G20" s="3">
         <v>-14300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1190,39 +1223,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-182400</v>
+        <v>-291900</v>
       </c>
       <c r="E21" s="3">
-        <v>-542700</v>
+        <v>-182600</v>
       </c>
       <c r="F21" s="3">
+        <v>-542200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-431100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-398200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-224800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-129000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1232,38 +1268,41 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E22" s="3">
         <v>21600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>21800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1274,39 +1313,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-282600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-158100</v>
       </c>
-      <c r="E23" s="3">
-        <v>-520100</v>
-      </c>
       <c r="F23" s="3">
+        <v>-520200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-445700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-407200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-308300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-127300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13800</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,39 +1358,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E24" s="3">
         <v>18900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-41900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-25700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4500</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1358,9 +1403,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,39 +1448,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-296800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-177000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-518300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-446300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-403600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-266400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-101600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9400</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1442,39 +1493,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-296800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-177000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-518300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-446400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-403600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-266400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-101600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9400</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1484,9 +1538,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1568,9 +1628,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,38 +1718,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-164800</v>
+      </c>
+      <c r="E32" s="3">
         <v>111800</v>
       </c>
-      <c r="E32" s="3">
-        <v>-111300</v>
-      </c>
       <c r="F32" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="G32" s="3">
         <v>14300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1694,39 +1763,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-296800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-177000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-518300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-446300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-403600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-266400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-101600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9400</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1736,9 +1808,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,39 +1853,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-296800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-177000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-518300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-446300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-403600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-266400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-101600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9400</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1820,44 +1898,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43831</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1867,9 +1948,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,38 +1989,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>901900</v>
+      </c>
+      <c r="E41" s="3">
         <v>286700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1277700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>786000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>688900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>455700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>83400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>210200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,38 +2031,41 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E42" s="3">
         <v>835900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>239600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>193500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>50000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>75600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -1987,39 +2076,42 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>124900</v>
+        <v>250300</v>
       </c>
       <c r="E43" s="3">
+        <v>125100</v>
+      </c>
+      <c r="F43" s="3">
         <v>157100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>44500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>82600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>30000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>108600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>228700</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2029,38 +2121,41 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E44" s="3">
         <v>23900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1100</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>0</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
@@ -2071,35 +2166,38 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
       </c>
       <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>300</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2113,39 +2211,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1247100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1283900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1497800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1099100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>949900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>593900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>212000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>327000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>230900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2155,27 +2256,30 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>4400</v>
       </c>
-      <c r="E47" s="3">
-        <v>4400</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>4700</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2197,39 +2301,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>401500</v>
+      </c>
+      <c r="E48" s="3">
         <v>201200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>189200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>160800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>140800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>111900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2239,38 +2346,41 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>4100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>500</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2281,9 +2391,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,36 +2481,39 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>178500</v>
+        <v>85100</v>
       </c>
       <c r="E52" s="3">
+        <v>185100</v>
+      </c>
+      <c r="F52" s="3">
         <v>153200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2407,9 +2526,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,39 +2571,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1733700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1670200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1848600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1331000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1119500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>722100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>292600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>429000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>238700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,9 +2616,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,38 +2657,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E57" s="3">
         <v>38600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2569,39 +2699,42 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>326500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,39 +2744,42 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>103900</v>
+      </c>
+      <c r="E59" s="3">
         <v>169800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>121000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>108600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>116900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>83600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>148800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2653,39 +2789,42 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>277600</v>
+        <v>636400</v>
       </c>
       <c r="E60" s="3">
+        <v>277700</v>
+      </c>
+      <c r="F60" s="3">
         <v>216400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>297800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>229200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>115600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>94200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>159200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,39 +2834,42 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E61" s="3">
         <v>345800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>325500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>281000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>122100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2737,30 +2879,33 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2779,9 +2924,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,39 +3059,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>731600</v>
+      </c>
+      <c r="E66" s="3">
         <v>629600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>597200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>586700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>353500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>124300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>141300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>420400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>226500</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2947,9 +3104,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,39 +3303,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1958500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1661700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1484700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-966500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-520100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-116500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>149800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,9 +3348,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,39 +3483,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1040500</v>
+        <v>1002100</v>
       </c>
       <c r="E76" s="3">
+        <v>1040600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1251400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>744300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>765900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>597800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>151300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3343,9 +3528,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,44 +3573,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43831</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3432,39 +3623,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-296800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-177000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-518300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-446300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-403600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-266400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-101600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9400</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,9 +3668,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,38 +3690,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E83" s="3">
         <v>21400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,9 +3732,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,39 +3957,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-144000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-393300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-201300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-198500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-223000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-83100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>307700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3786,9 +4002,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,38 +4024,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-42200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,9 +4066,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,39 +4156,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-850500</v>
+        <v>709600</v>
       </c>
       <c r="E94" s="3">
-        <v>92800</v>
+        <v>-850600</v>
       </c>
       <c r="F94" s="3">
+        <v>92900</v>
+      </c>
+      <c r="G94" s="3">
         <v>-77100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-195000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-102300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3972,9 +4201,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,8 +4223,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4032,9 +4265,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,39 +4400,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>5700</v>
       </c>
-      <c r="E100" s="3">
-        <v>791500</v>
-      </c>
       <c r="F100" s="3">
+        <v>791400</v>
+      </c>
+      <c r="G100" s="3">
         <v>378000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>626700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>618900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>14700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4200,38 +4445,41 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -4242,39 +4490,42 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>615200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-991000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>491700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>97100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>233200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>372300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-126800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>208100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,7 +4535,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
